--- a/outputs/reanalysis6/zones/mites.xlsx
+++ b/outputs/reanalysis6/zones/mites.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="dead" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="alive" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dead" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="alive" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -166,13 +166,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -191,13 +191,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -216,13 +216,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -241,13 +241,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -256,7 +256,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -271,13 +271,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -296,13 +296,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -321,13 +321,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -346,13 +346,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
